--- a/2026-ECMFA/RQ1/results/experiment_run_gpt-5-mini.xlsx
+++ b/2026-ECMFA/RQ1/results/experiment_run_gpt-5-mini.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\proyectos\emf-kaizen-experiments\2026-ECMFA\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyectos\emf-kaizen-experiments\2026-ECMFA\RQ1\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ECC5440-72D9-4EBF-A354-5F866A18942C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A57FA0F-C8EC-4DE9-A617-AF55239D2B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="eval run syntax" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="74">
   <si>
     <t>Meta-models</t>
   </si>
@@ -173,15 +173,6 @@
     <t>Missing reference</t>
   </si>
   <si>
-    <t>No response</t>
-  </si>
-  <si>
-    <t>Response shown as text in chat</t>
-  </si>
-  <si>
-    <t>Other errors</t>
-  </si>
-  <si>
     <t>Has some elements repeated from the current model, unnecesarily</t>
   </si>
   <si>
@@ -270,6 +261,9 @@
   </si>
   <si>
     <t>total</t>
+  </si>
+  <si>
+    <t>Incorrect intent</t>
   </si>
 </sst>
 </file>
@@ -812,36 +806,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -874,6 +838,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1209,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.36328125" customWidth="1"/>
@@ -1218,34 +1212,34 @@
     <col min="4" max="11" width="13.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D3" s="44" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D3" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="46" t="s">
+      <c r="E3" s="56"/>
+      <c r="F3" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="47"/>
-      <c r="H3" s="46" t="s">
+      <c r="G3" s="58"/>
+      <c r="H3" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="47"/>
-      <c r="J3" s="46" t="s">
+      <c r="I3" s="58"/>
+      <c r="J3" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="47"/>
-    </row>
-    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K3" s="58"/>
+    </row>
+    <row r="4" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1291,18 +1285,12 @@
       <c r="P4">
         <v>4</v>
       </c>
-      <c r="Q4">
-        <v>5</v>
-      </c>
-      <c r="R4">
-        <v>6</v>
-      </c>
-      <c r="S4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="41" t="s">
+      <c r="Q4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="52" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -1336,14 +1324,14 @@
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M5">
         <f>COUNTIF($D5:$K7,M4)</f>
         <v>18</v>
       </c>
       <c r="N5">
-        <f t="shared" ref="N5:R5" si="0">COUNTIF($D5:$K7,N4)</f>
+        <f t="shared" ref="N5:P5" si="0">COUNTIF($D5:$K7,N4)</f>
         <v>0</v>
       </c>
       <c r="O5">
@@ -1355,20 +1343,12 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <f>SUM(M5:R5)</f>
+        <f>SUM(M5:P5)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="42"/>
+    <row r="6" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="53"/>
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
@@ -1400,14 +1380,14 @@
         <v>3</v>
       </c>
       <c r="L6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M6">
         <f>100*M5/24</f>
         <v>75</v>
       </c>
       <c r="N6">
-        <f t="shared" ref="N6:R6" si="1">100*N5/24</f>
+        <f t="shared" ref="N6:P6" si="1">100*N5/24</f>
         <v>0</v>
       </c>
       <c r="O6">
@@ -1418,17 +1398,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="43"/>
+    </row>
+    <row r="7" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="54"/>
       <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
@@ -1460,8 +1432,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="48" t="s">
+    <row r="8" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="59" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1495,14 +1467,14 @@
         <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M8">
         <f>COUNTIF($D8:$K10,M4)</f>
         <v>24</v>
       </c>
       <c r="N8">
-        <f t="shared" ref="N8:R8" si="2">COUNTIF($D8:$K10,N4)</f>
+        <f t="shared" ref="N8:P8" si="2">COUNTIF($D8:$K10,N4)</f>
         <v>0</v>
       </c>
       <c r="O8">
@@ -1514,20 +1486,12 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <f>SUM(M8:R8)</f>
+        <f>SUM(M8:P8)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="49"/>
+    <row r="9" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="60"/>
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -1559,14 +1523,14 @@
         <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M9">
         <f>100*M8/24</f>
         <v>100</v>
       </c>
       <c r="N9">
-        <f t="shared" ref="N9:R9" si="3">100*N8/24</f>
+        <f t="shared" ref="N9:P9" si="3">100*N8/24</f>
         <v>0</v>
       </c>
       <c r="O9">
@@ -1577,17 +1541,9 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q9">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="50"/>
+    </row>
+    <row r="10" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="61"/>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
@@ -1619,8 +1575,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="41" t="s">
+    <row r="11" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -1654,14 +1610,14 @@
         <v>3</v>
       </c>
       <c r="L11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M11">
         <f>COUNTIF($D11:$K13,M4)</f>
         <v>20</v>
       </c>
       <c r="N11">
-        <f t="shared" ref="N11:R11" si="4">COUNTIF($D11:$K13,N4)</f>
+        <f t="shared" ref="N11:P11" si="4">COUNTIF($D11:$K13,N4)</f>
         <v>2</v>
       </c>
       <c r="O11">
@@ -1673,20 +1629,12 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <f>SUM(M11:R11)</f>
+        <f>SUM(M11:P11)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="42"/>
+    <row r="12" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="53"/>
       <c r="B12" s="5" t="s">
         <v>3</v>
       </c>
@@ -1718,14 +1666,14 @@
         <v>3</v>
       </c>
       <c r="L12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M12">
         <f>100*M11/24</f>
         <v>83.333333333333329</v>
       </c>
       <c r="N12">
-        <f t="shared" ref="N12:R12" si="5">100*N11/24</f>
+        <f t="shared" ref="N12:P12" si="5">100*N11/24</f>
         <v>8.3333333333333339</v>
       </c>
       <c r="O12">
@@ -1736,17 +1684,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q12">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="43"/>
+    </row>
+    <row r="13" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="54"/>
       <c r="B13" s="6" t="s">
         <v>4</v>
       </c>
@@ -1778,8 +1718,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="41" t="s">
+    <row r="14" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="52" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -1813,14 +1753,14 @@
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M14">
         <f>COUNTIF($D14:$K16,M4)</f>
         <v>24</v>
       </c>
       <c r="N14">
-        <f t="shared" ref="N14:R14" si="6">COUNTIF($D14:$K16,N4)</f>
+        <f t="shared" ref="N14:P14" si="6">COUNTIF($D14:$K16,N4)</f>
         <v>0</v>
       </c>
       <c r="O14">
@@ -1832,20 +1772,12 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <f>SUM(M14:R14)</f>
+        <f>SUM(M14:P14)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="42"/>
+    <row r="15" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="53"/>
       <c r="B15" s="5" t="s">
         <v>3</v>
       </c>
@@ -1877,14 +1809,14 @@
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M15">
         <f>100*M14/24</f>
         <v>100</v>
       </c>
       <c r="N15">
-        <f t="shared" ref="N15:R15" si="7">100*N14/24</f>
+        <f t="shared" ref="N15:P15" si="7">100*N14/24</f>
         <v>0</v>
       </c>
       <c r="O15">
@@ -1895,17 +1827,9 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Q15">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="43"/>
+    </row>
+    <row r="16" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="54"/>
       <c r="B16" s="6" t="s">
         <v>4</v>
       </c>
@@ -1937,8 +1861,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="41" t="s">
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="52" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -1972,14 +1896,14 @@
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M17">
         <f>COUNTIF($D17:$K19,M4)</f>
         <v>23</v>
       </c>
       <c r="N17">
-        <f t="shared" ref="N17:R17" si="8">COUNTIF($D17:$K19,N4)</f>
+        <f t="shared" ref="N17:P17" si="8">COUNTIF($D17:$K19,N4)</f>
         <v>0</v>
       </c>
       <c r="O17">
@@ -1991,20 +1915,12 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <f>SUM(M17:R17)</f>
+        <f>SUM(M17:P17)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="42"/>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="53"/>
       <c r="B18" s="5" t="s">
         <v>3</v>
       </c>
@@ -2036,14 +1952,14 @@
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M18">
         <f>100*M17/24</f>
         <v>95.833333333333329</v>
       </c>
       <c r="N18">
-        <f t="shared" ref="N18:R18" si="9">100*N17/24</f>
+        <f t="shared" ref="N18:P18" si="9">100*N17/24</f>
         <v>0</v>
       </c>
       <c r="O18">
@@ -2054,17 +1970,9 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="43"/>
+    </row>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="54"/>
       <c r="B19" s="6" t="s">
         <v>4</v>
       </c>
@@ -2096,15 +2004,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="E21" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -2123,7 +2031,7 @@
         <v>90.833333333333329</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B23">
         <v>2</v>
       </c>
@@ -2131,15 +2039,15 @@
         <v>41</v>
       </c>
       <c r="E23">
-        <f t="shared" ref="E23:E27" si="10">COUNTIF(D$5:K$19,B23)</f>
+        <f t="shared" ref="E23:E25" si="10">COUNTIF(D$5:K$19,B23)</f>
         <v>2</v>
       </c>
       <c r="F23">
-        <f t="shared" ref="F23:F27" si="11">100*E23/(15*8)</f>
+        <f t="shared" ref="F23:F25" si="11">100*E23/(15*8)</f>
         <v>1.6666666666666667</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B24">
         <v>3</v>
       </c>
@@ -2155,50 +2063,18 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B25">
         <v>4</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="E25">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F25">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B26">
-        <v>5</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B27">
-        <v>6</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F27">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -2235,27 +2111,27 @@
         <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="46" t="s">
+      <c r="E3" s="56"/>
+      <c r="F3" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="47"/>
-      <c r="H3" s="46" t="s">
+      <c r="G3" s="58"/>
+      <c r="H3" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="47"/>
-      <c r="J3" s="46" t="s">
+      <c r="I3" s="58"/>
+      <c r="J3" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="47"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
@@ -2292,14 +2168,14 @@
         <v>16</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="O4" s="37" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="52" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -2308,28 +2184,28 @@
       <c r="C5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="51">
-        <v>3</v>
-      </c>
-      <c r="E5" s="51">
-        <v>1</v>
-      </c>
-      <c r="F5" s="51">
-        <v>1</v>
-      </c>
-      <c r="G5" s="51">
-        <v>1</v>
-      </c>
-      <c r="H5" s="51">
-        <v>1</v>
-      </c>
-      <c r="I5" s="51">
-        <v>1</v>
-      </c>
-      <c r="J5" s="51">
-        <v>1</v>
-      </c>
-      <c r="K5" s="51">
+      <c r="D5" s="41">
+        <v>3</v>
+      </c>
+      <c r="E5" s="41">
+        <v>1</v>
+      </c>
+      <c r="F5" s="41">
+        <v>1</v>
+      </c>
+      <c r="G5" s="41">
+        <v>1</v>
+      </c>
+      <c r="H5" s="41">
+        <v>1</v>
+      </c>
+      <c r="I5" s="41">
+        <v>1</v>
+      </c>
+      <c r="J5" s="41">
+        <v>1</v>
+      </c>
+      <c r="K5" s="41">
         <v>1</v>
       </c>
       <c r="L5" s="1">
@@ -2348,42 +2224,42 @@
       </c>
     </row>
     <row r="6" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="42"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="52">
-        <v>1</v>
-      </c>
-      <c r="E6" s="52">
-        <v>1</v>
-      </c>
-      <c r="F6" s="52">
-        <v>1</v>
-      </c>
-      <c r="G6" s="52">
-        <v>1</v>
-      </c>
-      <c r="H6" s="52">
-        <v>1</v>
-      </c>
-      <c r="I6" s="52">
-        <v>1</v>
-      </c>
-      <c r="J6" s="52">
-        <v>1</v>
-      </c>
-      <c r="K6" s="52">
+      <c r="D6" s="42">
+        <v>1</v>
+      </c>
+      <c r="E6" s="42">
+        <v>1</v>
+      </c>
+      <c r="F6" s="42">
+        <v>1</v>
+      </c>
+      <c r="G6" s="42">
+        <v>1</v>
+      </c>
+      <c r="H6" s="42">
+        <v>1</v>
+      </c>
+      <c r="I6" s="42">
+        <v>1</v>
+      </c>
+      <c r="J6" s="42">
+        <v>1</v>
+      </c>
+      <c r="K6" s="42">
         <v>1</v>
       </c>
       <c r="L6" s="1">
         <v>2</v>
       </c>
       <c r="M6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N6">
         <f t="shared" ref="N6:N7" si="0">COUNTIF(D$5:K$7,L6)</f>
@@ -2395,42 +2271,42 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="43"/>
+      <c r="A7" s="54"/>
       <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="53">
-        <v>1</v>
-      </c>
-      <c r="E7" s="53">
-        <v>1</v>
-      </c>
-      <c r="F7" s="53">
-        <v>1</v>
-      </c>
-      <c r="G7" s="53">
-        <v>1</v>
-      </c>
-      <c r="H7" s="53">
-        <v>1</v>
-      </c>
-      <c r="I7" s="53">
-        <v>1</v>
-      </c>
-      <c r="J7" s="53">
-        <v>1</v>
-      </c>
-      <c r="K7" s="53">
+      <c r="D7" s="43">
+        <v>1</v>
+      </c>
+      <c r="E7" s="43">
+        <v>1</v>
+      </c>
+      <c r="F7" s="43">
+        <v>1</v>
+      </c>
+      <c r="G7" s="43">
+        <v>1</v>
+      </c>
+      <c r="H7" s="43">
+        <v>1</v>
+      </c>
+      <c r="I7" s="43">
+        <v>1</v>
+      </c>
+      <c r="J7" s="43">
+        <v>1</v>
+      </c>
+      <c r="K7" s="43">
         <v>1</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
@@ -2442,7 +2318,7 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="59" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -2451,28 +2327,28 @@
       <c r="C8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="51">
-        <v>3</v>
-      </c>
-      <c r="E8" s="52">
-        <v>3</v>
-      </c>
-      <c r="F8" s="51">
-        <v>1</v>
-      </c>
-      <c r="G8" s="51">
-        <v>1</v>
-      </c>
-      <c r="H8" s="51">
-        <v>3</v>
-      </c>
-      <c r="I8" s="51">
-        <v>1</v>
-      </c>
-      <c r="J8" s="51">
-        <v>3</v>
-      </c>
-      <c r="K8" s="51">
+      <c r="D8" s="41">
+        <v>3</v>
+      </c>
+      <c r="E8" s="42">
+        <v>3</v>
+      </c>
+      <c r="F8" s="41">
+        <v>1</v>
+      </c>
+      <c r="G8" s="41">
+        <v>1</v>
+      </c>
+      <c r="H8" s="41">
+        <v>3</v>
+      </c>
+      <c r="I8" s="41">
+        <v>1</v>
+      </c>
+      <c r="J8" s="41">
+        <v>3</v>
+      </c>
+      <c r="K8" s="41">
         <v>1</v>
       </c>
       <c r="L8" s="1">
@@ -2491,42 +2367,42 @@
       </c>
     </row>
     <row r="9" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="49"/>
+      <c r="A9" s="60"/>
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="52">
-        <v>1</v>
-      </c>
-      <c r="E9" s="52">
-        <v>1</v>
-      </c>
-      <c r="F9" s="52">
-        <v>1</v>
-      </c>
-      <c r="G9" s="52">
-        <v>1</v>
-      </c>
-      <c r="H9" s="52">
-        <v>1</v>
-      </c>
-      <c r="I9" s="52">
-        <v>1</v>
-      </c>
-      <c r="J9" s="52">
-        <v>2</v>
-      </c>
-      <c r="K9" s="52">
+      <c r="D9" s="42">
+        <v>1</v>
+      </c>
+      <c r="E9" s="42">
+        <v>1</v>
+      </c>
+      <c r="F9" s="42">
+        <v>1</v>
+      </c>
+      <c r="G9" s="42">
+        <v>1</v>
+      </c>
+      <c r="H9" s="42">
+        <v>1</v>
+      </c>
+      <c r="I9" s="42">
+        <v>1</v>
+      </c>
+      <c r="J9" s="42">
+        <v>2</v>
+      </c>
+      <c r="K9" s="42">
         <v>2</v>
       </c>
       <c r="L9" s="1">
         <v>2</v>
       </c>
       <c r="M9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N9">
         <f t="shared" ref="N9:N10" si="2">COUNTIF(D$8:K$10,L9)</f>
@@ -2538,42 +2414,42 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="50"/>
+      <c r="A10" s="61"/>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="53">
-        <v>1</v>
-      </c>
-      <c r="E10" s="52">
-        <v>1</v>
-      </c>
-      <c r="F10" s="53">
-        <v>1</v>
-      </c>
-      <c r="G10" s="53">
-        <v>1</v>
-      </c>
-      <c r="H10" s="53">
-        <v>2</v>
-      </c>
-      <c r="I10" s="53">
-        <v>1</v>
-      </c>
-      <c r="J10" s="53">
-        <v>1</v>
-      </c>
-      <c r="K10" s="53">
+      <c r="D10" s="43">
+        <v>1</v>
+      </c>
+      <c r="E10" s="42">
+        <v>1</v>
+      </c>
+      <c r="F10" s="43">
+        <v>1</v>
+      </c>
+      <c r="G10" s="43">
+        <v>1</v>
+      </c>
+      <c r="H10" s="43">
+        <v>2</v>
+      </c>
+      <c r="I10" s="43">
+        <v>1</v>
+      </c>
+      <c r="J10" s="43">
+        <v>1</v>
+      </c>
+      <c r="K10" s="43">
         <v>1</v>
       </c>
       <c r="L10" s="1">
         <v>3</v>
       </c>
       <c r="M10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N10">
         <f t="shared" si="2"/>
@@ -2585,7 +2461,7 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -2594,28 +2470,28 @@
       <c r="C11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="52">
-        <v>3</v>
-      </c>
-      <c r="E11" s="51">
-        <v>1</v>
-      </c>
-      <c r="F11" s="51">
-        <v>1</v>
-      </c>
-      <c r="G11" s="51">
-        <v>1</v>
-      </c>
-      <c r="H11" s="51">
-        <v>1</v>
-      </c>
-      <c r="I11" s="51">
-        <v>1</v>
-      </c>
-      <c r="J11" s="51">
-        <v>1</v>
-      </c>
-      <c r="K11" s="51">
+      <c r="D11" s="42">
+        <v>3</v>
+      </c>
+      <c r="E11" s="41">
+        <v>1</v>
+      </c>
+      <c r="F11" s="41">
+        <v>1</v>
+      </c>
+      <c r="G11" s="41">
+        <v>1</v>
+      </c>
+      <c r="H11" s="41">
+        <v>1</v>
+      </c>
+      <c r="I11" s="41">
+        <v>1</v>
+      </c>
+      <c r="J11" s="41">
+        <v>1</v>
+      </c>
+      <c r="K11" s="41">
         <v>1</v>
       </c>
       <c r="L11" s="1">
@@ -2634,42 +2510,42 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="42"/>
+      <c r="A12" s="53"/>
       <c r="B12" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="52">
-        <v>1</v>
-      </c>
-      <c r="E12" s="52">
-        <v>1</v>
-      </c>
-      <c r="F12" s="52">
-        <v>1</v>
-      </c>
-      <c r="G12" s="52">
-        <v>1</v>
-      </c>
-      <c r="H12" s="52">
-        <v>2</v>
-      </c>
-      <c r="I12" s="52">
-        <v>1</v>
-      </c>
-      <c r="J12" s="52">
-        <v>2</v>
-      </c>
-      <c r="K12" s="52">
+      <c r="D12" s="42">
+        <v>1</v>
+      </c>
+      <c r="E12" s="42">
+        <v>1</v>
+      </c>
+      <c r="F12" s="42">
+        <v>1</v>
+      </c>
+      <c r="G12" s="42">
+        <v>1</v>
+      </c>
+      <c r="H12" s="42">
+        <v>2</v>
+      </c>
+      <c r="I12" s="42">
+        <v>1</v>
+      </c>
+      <c r="J12" s="42">
+        <v>2</v>
+      </c>
+      <c r="K12" s="42">
         <v>1</v>
       </c>
       <c r="L12" s="1">
         <v>2</v>
       </c>
       <c r="M12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N12">
         <f t="shared" ref="N12:N13" si="3">COUNTIF(D$11:K$13,L12)</f>
@@ -2681,42 +2557,42 @@
       </c>
     </row>
     <row r="13" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="43"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="54">
-        <v>1</v>
-      </c>
-      <c r="E13" s="54">
-        <v>1</v>
-      </c>
-      <c r="F13" s="53">
-        <v>1</v>
-      </c>
-      <c r="G13" s="53">
-        <v>1</v>
-      </c>
-      <c r="H13" s="53">
-        <v>1</v>
-      </c>
-      <c r="I13" s="53">
-        <v>1</v>
-      </c>
-      <c r="J13" s="53">
-        <v>1</v>
-      </c>
-      <c r="K13" s="53">
+      <c r="D13" s="44">
+        <v>1</v>
+      </c>
+      <c r="E13" s="44">
+        <v>1</v>
+      </c>
+      <c r="F13" s="43">
+        <v>1</v>
+      </c>
+      <c r="G13" s="43">
+        <v>1</v>
+      </c>
+      <c r="H13" s="43">
+        <v>1</v>
+      </c>
+      <c r="I13" s="43">
+        <v>1</v>
+      </c>
+      <c r="J13" s="43">
+        <v>1</v>
+      </c>
+      <c r="K13" s="43">
         <v>1</v>
       </c>
       <c r="L13" s="1">
         <v>3</v>
       </c>
       <c r="M13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N13">
         <f t="shared" si="3"/>
@@ -2728,7 +2604,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="52" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -2737,28 +2613,28 @@
       <c r="C14" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="51">
-        <v>1</v>
-      </c>
-      <c r="E14" s="51">
-        <v>1</v>
-      </c>
-      <c r="F14" s="51">
-        <v>1</v>
-      </c>
-      <c r="G14" s="55">
-        <v>1</v>
-      </c>
-      <c r="H14" s="51">
-        <v>1</v>
-      </c>
-      <c r="I14" s="51">
-        <v>1</v>
-      </c>
-      <c r="J14" s="51">
-        <v>1</v>
-      </c>
-      <c r="K14" s="51">
+      <c r="D14" s="41">
+        <v>1</v>
+      </c>
+      <c r="E14" s="41">
+        <v>1</v>
+      </c>
+      <c r="F14" s="41">
+        <v>1</v>
+      </c>
+      <c r="G14" s="45">
+        <v>1</v>
+      </c>
+      <c r="H14" s="41">
+        <v>1</v>
+      </c>
+      <c r="I14" s="41">
+        <v>1</v>
+      </c>
+      <c r="J14" s="41">
+        <v>1</v>
+      </c>
+      <c r="K14" s="41">
         <v>1</v>
       </c>
       <c r="L14" s="1">
@@ -2777,42 +2653,42 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="42"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="52">
-        <v>3</v>
-      </c>
-      <c r="E15" s="52">
-        <v>3</v>
-      </c>
-      <c r="F15" s="52">
-        <v>1</v>
-      </c>
-      <c r="G15" s="56">
-        <v>1</v>
-      </c>
-      <c r="H15" s="52">
-        <v>1</v>
-      </c>
-      <c r="I15" s="52">
-        <v>1</v>
-      </c>
-      <c r="J15" s="52">
-        <v>3</v>
-      </c>
-      <c r="K15" s="52">
+      <c r="D15" s="42">
+        <v>3</v>
+      </c>
+      <c r="E15" s="42">
+        <v>3</v>
+      </c>
+      <c r="F15" s="42">
+        <v>1</v>
+      </c>
+      <c r="G15" s="46">
+        <v>1</v>
+      </c>
+      <c r="H15" s="42">
+        <v>1</v>
+      </c>
+      <c r="I15" s="42">
+        <v>1</v>
+      </c>
+      <c r="J15" s="42">
+        <v>3</v>
+      </c>
+      <c r="K15" s="42">
         <v>3</v>
       </c>
       <c r="L15" s="1">
         <v>2</v>
       </c>
       <c r="M15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N15">
         <f t="shared" ref="N15:N16" si="4">COUNTIF(D$14:K$16,L15)</f>
@@ -2824,42 +2700,42 @@
       </c>
     </row>
     <row r="16" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="43"/>
+      <c r="A16" s="54"/>
       <c r="B16" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="53">
-        <v>1</v>
-      </c>
-      <c r="E16" s="53">
-        <v>1</v>
-      </c>
-      <c r="F16" s="53">
-        <v>1</v>
-      </c>
-      <c r="G16" s="57">
-        <v>1</v>
-      </c>
-      <c r="H16" s="53">
-        <v>1</v>
-      </c>
-      <c r="I16" s="53">
-        <v>1</v>
-      </c>
-      <c r="J16" s="53">
-        <v>1</v>
-      </c>
-      <c r="K16" s="53">
+      <c r="D16" s="43">
+        <v>1</v>
+      </c>
+      <c r="E16" s="43">
+        <v>1</v>
+      </c>
+      <c r="F16" s="43">
+        <v>1</v>
+      </c>
+      <c r="G16" s="47">
+        <v>1</v>
+      </c>
+      <c r="H16" s="43">
+        <v>1</v>
+      </c>
+      <c r="I16" s="43">
+        <v>1</v>
+      </c>
+      <c r="J16" s="43">
+        <v>1</v>
+      </c>
+      <c r="K16" s="43">
         <v>2</v>
       </c>
       <c r="L16" s="1">
         <v>3</v>
       </c>
       <c r="M16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N16">
         <f t="shared" si="4"/>
@@ -2871,7 +2747,7 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="52" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -2880,28 +2756,28 @@
       <c r="C17" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="58">
-        <v>1</v>
-      </c>
-      <c r="E17" s="58">
-        <v>3</v>
-      </c>
-      <c r="F17" s="51">
-        <v>1</v>
-      </c>
-      <c r="G17" s="55">
-        <v>3</v>
-      </c>
-      <c r="H17" s="51">
-        <v>1</v>
-      </c>
-      <c r="I17" s="51">
-        <v>1</v>
-      </c>
-      <c r="J17" s="51">
-        <v>1</v>
-      </c>
-      <c r="K17" s="51">
+      <c r="D17" s="48">
+        <v>1</v>
+      </c>
+      <c r="E17" s="48">
+        <v>3</v>
+      </c>
+      <c r="F17" s="41">
+        <v>1</v>
+      </c>
+      <c r="G17" s="45">
+        <v>3</v>
+      </c>
+      <c r="H17" s="41">
+        <v>1</v>
+      </c>
+      <c r="I17" s="41">
+        <v>1</v>
+      </c>
+      <c r="J17" s="41">
+        <v>1</v>
+      </c>
+      <c r="K17" s="41">
         <v>1</v>
       </c>
       <c r="L17" s="1">
@@ -2920,42 +2796,42 @@
       </c>
     </row>
     <row r="18" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="42"/>
+      <c r="A18" s="53"/>
       <c r="B18" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="52">
-        <v>1</v>
-      </c>
-      <c r="E18" s="52">
-        <v>1</v>
-      </c>
-      <c r="F18" s="52">
-        <v>1</v>
-      </c>
-      <c r="G18" s="56">
-        <v>1</v>
-      </c>
-      <c r="H18" s="52">
-        <v>1</v>
-      </c>
-      <c r="I18" s="52">
-        <v>1</v>
-      </c>
-      <c r="J18" s="52">
-        <v>3</v>
-      </c>
-      <c r="K18" s="52">
+      <c r="D18" s="42">
+        <v>1</v>
+      </c>
+      <c r="E18" s="42">
+        <v>1</v>
+      </c>
+      <c r="F18" s="42">
+        <v>1</v>
+      </c>
+      <c r="G18" s="46">
+        <v>1</v>
+      </c>
+      <c r="H18" s="42">
+        <v>1</v>
+      </c>
+      <c r="I18" s="42">
+        <v>1</v>
+      </c>
+      <c r="J18" s="42">
+        <v>3</v>
+      </c>
+      <c r="K18" s="42">
         <v>1</v>
       </c>
       <c r="L18" s="1">
         <v>2</v>
       </c>
       <c r="M18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N18">
         <f t="shared" ref="N18:N19" si="5">COUNTIF(D$17:K$19,L18)</f>
@@ -2967,42 +2843,42 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="43"/>
+      <c r="A19" s="54"/>
       <c r="B19" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="53">
-        <v>1</v>
-      </c>
-      <c r="E19" s="53">
-        <v>1</v>
-      </c>
-      <c r="F19" s="53">
-        <v>1</v>
-      </c>
-      <c r="G19" s="57">
-        <v>1</v>
-      </c>
-      <c r="H19" s="53">
-        <v>1</v>
-      </c>
-      <c r="I19" s="53">
-        <v>1</v>
-      </c>
-      <c r="J19" s="53">
-        <v>1</v>
-      </c>
-      <c r="K19" s="53">
+      <c r="D19" s="43">
+        <v>1</v>
+      </c>
+      <c r="E19" s="43">
+        <v>1</v>
+      </c>
+      <c r="F19" s="43">
+        <v>1</v>
+      </c>
+      <c r="G19" s="47">
+        <v>1</v>
+      </c>
+      <c r="H19" s="43">
+        <v>1</v>
+      </c>
+      <c r="I19" s="43">
+        <v>1</v>
+      </c>
+      <c r="J19" s="43">
+        <v>1</v>
+      </c>
+      <c r="K19" s="43">
         <v>1</v>
       </c>
       <c r="L19" s="1">
         <v>3</v>
       </c>
       <c r="M19" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N19">
         <f t="shared" si="5"/>
@@ -3015,10 +2891,10 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="F21" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G21" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
@@ -3045,7 +2921,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F23">
         <f>COUNTIF(D$5:K$19,B23)</f>
@@ -3061,7 +2937,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F24">
         <f>COUNTIF(D$5:K$19,B24)</f>
@@ -3104,27 +2980,27 @@
         <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="46" t="s">
+      <c r="E3" s="56"/>
+      <c r="F3" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="47"/>
-      <c r="H3" s="46" t="s">
+      <c r="G3" s="58"/>
+      <c r="H3" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="47"/>
-      <c r="J3" s="46" t="s">
+      <c r="I3" s="58"/>
+      <c r="J3" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="47"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
@@ -3161,14 +3037,14 @@
         <v>16</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O4" s="37" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="52" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -3205,7 +3081,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N5">
         <f>COUNTIF(D$5:K$7,L5)</f>
@@ -3217,7 +3093,7 @@
       </c>
     </row>
     <row r="6" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="42"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
@@ -3252,7 +3128,7 @@
         <v>2</v>
       </c>
       <c r="M6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N6">
         <f t="shared" ref="N6:N7" si="0">COUNTIF(D$5:K$7,L6)</f>
@@ -3264,7 +3140,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="43"/>
+      <c r="A7" s="54"/>
       <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
@@ -3299,7 +3175,7 @@
         <v>3</v>
       </c>
       <c r="M7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
@@ -3311,7 +3187,7 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="59" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -3348,7 +3224,7 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N8">
         <f>COUNTIF(D$8:K$10,L8)</f>
@@ -3360,7 +3236,7 @@
       </c>
     </row>
     <row r="9" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="49"/>
+      <c r="A9" s="60"/>
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -3395,7 +3271,7 @@
         <v>2</v>
       </c>
       <c r="M9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N9">
         <f t="shared" ref="N9:N10" si="2">COUNTIF(D$8:K$10,L9)</f>
@@ -3407,7 +3283,7 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="50"/>
+      <c r="A10" s="61"/>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
@@ -3442,7 +3318,7 @@
         <v>3</v>
       </c>
       <c r="M10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N10">
         <f t="shared" si="2"/>
@@ -3454,7 +3330,7 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -3491,7 +3367,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N11">
         <f>COUNTIF(D$11:K$13,L11)</f>
@@ -3503,7 +3379,7 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="42"/>
+      <c r="A12" s="53"/>
       <c r="B12" s="5" t="s">
         <v>3</v>
       </c>
@@ -3538,7 +3414,7 @@
         <v>2</v>
       </c>
       <c r="M12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N12">
         <f t="shared" ref="N12:N13" si="3">COUNTIF(D$11:K$13,L12)</f>
@@ -3550,7 +3426,7 @@
       </c>
     </row>
     <row r="13" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="43"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="6" t="s">
         <v>4</v>
       </c>
@@ -3585,7 +3461,7 @@
         <v>3</v>
       </c>
       <c r="M13" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N13">
         <f t="shared" si="3"/>
@@ -3597,7 +3473,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="52" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -3634,7 +3510,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N14">
         <f>COUNTIF(D$14:K$16,L14)</f>
@@ -3646,7 +3522,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="42"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="5" t="s">
         <v>3</v>
       </c>
@@ -3681,7 +3557,7 @@
         <v>2</v>
       </c>
       <c r="M15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N15">
         <f t="shared" ref="N15:N16" si="4">COUNTIF(D$14:K$16,L15)</f>
@@ -3693,7 +3569,7 @@
       </c>
     </row>
     <row r="16" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="43"/>
+      <c r="A16" s="54"/>
       <c r="B16" s="6" t="s">
         <v>4</v>
       </c>
@@ -3728,7 +3604,7 @@
         <v>3</v>
       </c>
       <c r="M16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N16">
         <f t="shared" si="4"/>
@@ -3740,7 +3616,7 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="52" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -3777,7 +3653,7 @@
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N17">
         <f>COUNTIF(D$17:K$19,L17)</f>
@@ -3789,7 +3665,7 @@
       </c>
     </row>
     <row r="18" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="42"/>
+      <c r="A18" s="53"/>
       <c r="B18" s="5" t="s">
         <v>3</v>
       </c>
@@ -3824,7 +3700,7 @@
         <v>2</v>
       </c>
       <c r="M18" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N18">
         <f t="shared" ref="N18:N19" si="5">COUNTIF(D$17:K$19,L18)</f>
@@ -3836,7 +3712,7 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="43"/>
+      <c r="A19" s="54"/>
       <c r="B19" s="6" t="s">
         <v>4</v>
       </c>
@@ -3871,7 +3747,7 @@
         <v>3</v>
       </c>
       <c r="M19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N19">
         <f t="shared" si="5"/>
@@ -3884,10 +3760,10 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D21" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E21" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
@@ -3898,7 +3774,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D22">
         <f>COUNTIF(D$5:K$19,B22)</f>
@@ -3914,7 +3790,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D23">
         <f t="shared" ref="D23:D24" si="6">COUNTIF(D$5:K$19,B23)</f>
@@ -3930,7 +3806,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D24">
         <f t="shared" si="6"/>
@@ -3974,29 +3850,29 @@
         <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="46" t="s">
+      <c r="E3" s="56"/>
+      <c r="F3" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="47"/>
-      <c r="H3" s="46" t="s">
+      <c r="G3" s="58"/>
+      <c r="H3" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="47"/>
-      <c r="J3" s="46" t="s">
+      <c r="I3" s="58"/>
+      <c r="J3" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="47"/>
+      <c r="K3" s="58"/>
       <c r="M3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4037,17 +3913,17 @@
         <v>8</v>
       </c>
       <c r="N4" s="40" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O4" s="40" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="P4" s="40" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="52" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -4056,28 +3932,28 @@
       <c r="C5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="51">
-        <v>3</v>
-      </c>
-      <c r="E5" s="51">
-        <v>3</v>
-      </c>
-      <c r="F5" s="51">
-        <v>3</v>
-      </c>
-      <c r="G5" s="51">
-        <v>3</v>
-      </c>
-      <c r="H5" s="51">
-        <v>3</v>
-      </c>
-      <c r="I5" s="59">
-        <v>3</v>
-      </c>
-      <c r="J5" s="51">
-        <v>3</v>
-      </c>
-      <c r="K5" s="51">
+      <c r="D5" s="41">
+        <v>3</v>
+      </c>
+      <c r="E5" s="41">
+        <v>3</v>
+      </c>
+      <c r="F5" s="41">
+        <v>3</v>
+      </c>
+      <c r="G5" s="41">
+        <v>3</v>
+      </c>
+      <c r="H5" s="41">
+        <v>3</v>
+      </c>
+      <c r="I5" s="49">
+        <v>3</v>
+      </c>
+      <c r="J5" s="41">
+        <v>3</v>
+      </c>
+      <c r="K5" s="41">
         <v>3</v>
       </c>
       <c r="L5" s="1">
@@ -4101,35 +3977,35 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="42"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="52">
-        <v>3</v>
-      </c>
-      <c r="E6" s="52">
-        <v>3</v>
-      </c>
-      <c r="F6" s="52">
-        <v>3</v>
-      </c>
-      <c r="G6" s="52">
-        <v>2</v>
-      </c>
-      <c r="H6" s="52">
-        <v>3</v>
-      </c>
-      <c r="I6" s="52">
-        <v>3</v>
-      </c>
-      <c r="J6" s="52">
-        <v>3</v>
-      </c>
-      <c r="K6" s="52">
+      <c r="D6" s="42">
+        <v>3</v>
+      </c>
+      <c r="E6" s="42">
+        <v>3</v>
+      </c>
+      <c r="F6" s="42">
+        <v>3</v>
+      </c>
+      <c r="G6" s="42">
+        <v>2</v>
+      </c>
+      <c r="H6" s="42">
+        <v>3</v>
+      </c>
+      <c r="I6" s="42">
+        <v>3</v>
+      </c>
+      <c r="J6" s="42">
+        <v>3</v>
+      </c>
+      <c r="K6" s="42">
         <v>3</v>
       </c>
       <c r="L6" s="1">
@@ -4153,35 +4029,35 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="43"/>
+      <c r="A7" s="54"/>
       <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="53">
-        <v>3</v>
-      </c>
-      <c r="E7" s="53">
-        <v>3</v>
-      </c>
-      <c r="F7" s="53">
-        <v>3</v>
-      </c>
-      <c r="G7" s="53">
-        <v>3</v>
-      </c>
-      <c r="H7" s="53">
-        <v>3</v>
-      </c>
-      <c r="I7" s="53">
-        <v>3</v>
-      </c>
-      <c r="J7" s="53">
-        <v>3</v>
-      </c>
-      <c r="K7" s="53">
+      <c r="D7" s="43">
+        <v>3</v>
+      </c>
+      <c r="E7" s="43">
+        <v>3</v>
+      </c>
+      <c r="F7" s="43">
+        <v>3</v>
+      </c>
+      <c r="G7" s="43">
+        <v>3</v>
+      </c>
+      <c r="H7" s="43">
+        <v>3</v>
+      </c>
+      <c r="I7" s="43">
+        <v>3</v>
+      </c>
+      <c r="J7" s="43">
+        <v>3</v>
+      </c>
+      <c r="K7" s="43">
         <v>3</v>
       </c>
       <c r="L7" s="1">
@@ -4205,7 +4081,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="59" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -4214,32 +4090,32 @@
       <c r="C8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="51">
-        <v>3</v>
-      </c>
-      <c r="E8" s="52">
-        <v>3</v>
-      </c>
-      <c r="F8" s="51">
-        <v>3</v>
-      </c>
-      <c r="G8" s="51">
-        <v>3</v>
-      </c>
-      <c r="H8" s="51">
-        <v>3</v>
-      </c>
-      <c r="I8" s="51">
-        <v>3</v>
-      </c>
-      <c r="J8" s="59">
-        <v>3</v>
-      </c>
-      <c r="K8" s="51">
+      <c r="D8" s="41">
+        <v>3</v>
+      </c>
+      <c r="E8" s="42">
+        <v>3</v>
+      </c>
+      <c r="F8" s="41">
+        <v>3</v>
+      </c>
+      <c r="G8" s="41">
+        <v>3</v>
+      </c>
+      <c r="H8" s="41">
+        <v>3</v>
+      </c>
+      <c r="I8" s="41">
+        <v>3</v>
+      </c>
+      <c r="J8" s="49">
+        <v>3</v>
+      </c>
+      <c r="K8" s="41">
         <v>3</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="M8">
         <f>SUM(M5:M7)</f>
@@ -4259,75 +4135,75 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="49"/>
+      <c r="A9" s="60"/>
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="52">
-        <v>3</v>
-      </c>
-      <c r="E9" s="52">
-        <v>3</v>
-      </c>
-      <c r="F9" s="52">
-        <v>3</v>
-      </c>
-      <c r="G9" s="52">
-        <v>3</v>
-      </c>
-      <c r="H9" s="52">
-        <v>3</v>
-      </c>
-      <c r="I9" s="52">
-        <v>3</v>
-      </c>
-      <c r="J9" s="60">
-        <v>3</v>
-      </c>
-      <c r="K9" s="52">
+      <c r="D9" s="42">
+        <v>3</v>
+      </c>
+      <c r="E9" s="42">
+        <v>3</v>
+      </c>
+      <c r="F9" s="42">
+        <v>3</v>
+      </c>
+      <c r="G9" s="42">
+        <v>3</v>
+      </c>
+      <c r="H9" s="42">
+        <v>3</v>
+      </c>
+      <c r="I9" s="42">
+        <v>3</v>
+      </c>
+      <c r="J9" s="50">
+        <v>3</v>
+      </c>
+      <c r="K9" s="42">
         <v>3</v>
       </c>
       <c r="L9" s="1"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="50"/>
+      <c r="A10" s="61"/>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="53">
-        <v>3</v>
-      </c>
-      <c r="E10" s="52">
-        <v>3</v>
-      </c>
-      <c r="F10" s="53">
-        <v>3</v>
-      </c>
-      <c r="G10" s="53">
-        <v>3</v>
-      </c>
-      <c r="H10" s="53">
-        <v>3</v>
-      </c>
-      <c r="I10" s="53">
-        <v>3</v>
-      </c>
-      <c r="J10" s="61">
-        <v>3</v>
-      </c>
-      <c r="K10" s="53">
+      <c r="D10" s="43">
+        <v>3</v>
+      </c>
+      <c r="E10" s="42">
+        <v>3</v>
+      </c>
+      <c r="F10" s="43">
+        <v>3</v>
+      </c>
+      <c r="G10" s="43">
+        <v>3</v>
+      </c>
+      <c r="H10" s="43">
+        <v>3</v>
+      </c>
+      <c r="I10" s="43">
+        <v>3</v>
+      </c>
+      <c r="J10" s="51">
+        <v>3</v>
+      </c>
+      <c r="K10" s="43">
         <v>2</v>
       </c>
       <c r="L10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -4336,102 +4212,102 @@
       <c r="C11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="52">
-        <v>3</v>
-      </c>
-      <c r="E11" s="51">
-        <v>3</v>
-      </c>
-      <c r="F11" s="51">
-        <v>3</v>
-      </c>
-      <c r="G11" s="51">
-        <v>3</v>
-      </c>
-      <c r="H11" s="51">
-        <v>3</v>
-      </c>
-      <c r="I11" s="59">
-        <v>3</v>
-      </c>
-      <c r="J11" s="51">
-        <v>3</v>
-      </c>
-      <c r="K11" s="51">
+      <c r="D11" s="42">
+        <v>3</v>
+      </c>
+      <c r="E11" s="41">
+        <v>3</v>
+      </c>
+      <c r="F11" s="41">
+        <v>3</v>
+      </c>
+      <c r="G11" s="41">
+        <v>3</v>
+      </c>
+      <c r="H11" s="41">
+        <v>3</v>
+      </c>
+      <c r="I11" s="49">
+        <v>3</v>
+      </c>
+      <c r="J11" s="41">
+        <v>3</v>
+      </c>
+      <c r="K11" s="41">
         <v>3</v>
       </c>
       <c r="L11" s="1"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="42"/>
+      <c r="A12" s="53"/>
       <c r="B12" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="52">
-        <v>3</v>
-      </c>
-      <c r="E12" s="52">
-        <v>3</v>
-      </c>
-      <c r="F12" s="52">
-        <v>3</v>
-      </c>
-      <c r="G12" s="52">
-        <v>3</v>
-      </c>
-      <c r="H12" s="52">
-        <v>3</v>
-      </c>
-      <c r="I12" s="60">
-        <v>3</v>
-      </c>
-      <c r="J12" s="52">
-        <v>2</v>
-      </c>
-      <c r="K12" s="52">
+      <c r="D12" s="42">
+        <v>3</v>
+      </c>
+      <c r="E12" s="42">
+        <v>3</v>
+      </c>
+      <c r="F12" s="42">
+        <v>3</v>
+      </c>
+      <c r="G12" s="42">
+        <v>3</v>
+      </c>
+      <c r="H12" s="42">
+        <v>3</v>
+      </c>
+      <c r="I12" s="50">
+        <v>3</v>
+      </c>
+      <c r="J12" s="42">
+        <v>2</v>
+      </c>
+      <c r="K12" s="42">
         <v>2</v>
       </c>
       <c r="L12" s="1"/>
     </row>
     <row r="13" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="43"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="54">
-        <v>3</v>
-      </c>
-      <c r="E13" s="54">
-        <v>3</v>
-      </c>
-      <c r="F13" s="53">
-        <v>3</v>
-      </c>
-      <c r="G13" s="53">
-        <v>3</v>
-      </c>
-      <c r="H13" s="53">
-        <v>3</v>
-      </c>
-      <c r="I13" s="61">
-        <v>3</v>
-      </c>
-      <c r="J13" s="53">
-        <v>3</v>
-      </c>
-      <c r="K13" s="53">
+      <c r="D13" s="44">
+        <v>3</v>
+      </c>
+      <c r="E13" s="44">
+        <v>3</v>
+      </c>
+      <c r="F13" s="43">
+        <v>3</v>
+      </c>
+      <c r="G13" s="43">
+        <v>3</v>
+      </c>
+      <c r="H13" s="43">
+        <v>3</v>
+      </c>
+      <c r="I13" s="51">
+        <v>3</v>
+      </c>
+      <c r="J13" s="43">
+        <v>3</v>
+      </c>
+      <c r="K13" s="43">
         <v>2</v>
       </c>
       <c r="L13" s="1"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="52" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -4440,102 +4316,102 @@
       <c r="C14" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="51">
-        <v>3</v>
-      </c>
-      <c r="E14" s="51">
-        <v>3</v>
-      </c>
-      <c r="F14" s="51">
-        <v>3</v>
-      </c>
-      <c r="G14" s="55">
-        <v>3</v>
-      </c>
-      <c r="H14" s="51">
-        <v>3</v>
-      </c>
-      <c r="I14" s="59">
-        <v>3</v>
-      </c>
-      <c r="J14" s="51">
-        <v>3</v>
-      </c>
-      <c r="K14" s="51">
+      <c r="D14" s="41">
+        <v>3</v>
+      </c>
+      <c r="E14" s="41">
+        <v>3</v>
+      </c>
+      <c r="F14" s="41">
+        <v>3</v>
+      </c>
+      <c r="G14" s="45">
+        <v>3</v>
+      </c>
+      <c r="H14" s="41">
+        <v>3</v>
+      </c>
+      <c r="I14" s="49">
+        <v>3</v>
+      </c>
+      <c r="J14" s="41">
+        <v>3</v>
+      </c>
+      <c r="K14" s="41">
         <v>3</v>
       </c>
       <c r="L14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="42"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="52">
-        <v>3</v>
-      </c>
-      <c r="E15" s="52">
-        <v>3</v>
-      </c>
-      <c r="F15" s="52">
-        <v>3</v>
-      </c>
-      <c r="G15" s="56">
-        <v>2</v>
-      </c>
-      <c r="H15" s="52">
-        <v>3</v>
-      </c>
-      <c r="I15" s="60">
-        <v>3</v>
-      </c>
-      <c r="J15" s="52">
-        <v>2</v>
-      </c>
-      <c r="K15" s="52">
+      <c r="D15" s="42">
+        <v>3</v>
+      </c>
+      <c r="E15" s="42">
+        <v>3</v>
+      </c>
+      <c r="F15" s="42">
+        <v>3</v>
+      </c>
+      <c r="G15" s="46">
+        <v>2</v>
+      </c>
+      <c r="H15" s="42">
+        <v>3</v>
+      </c>
+      <c r="I15" s="50">
+        <v>3</v>
+      </c>
+      <c r="J15" s="42">
+        <v>2</v>
+      </c>
+      <c r="K15" s="42">
         <v>3</v>
       </c>
       <c r="L15" s="1"/>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="43"/>
+      <c r="A16" s="54"/>
       <c r="B16" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="53">
-        <v>3</v>
-      </c>
-      <c r="E16" s="53">
-        <v>3</v>
-      </c>
-      <c r="F16" s="53">
-        <v>3</v>
-      </c>
-      <c r="G16" s="53">
-        <v>3</v>
-      </c>
-      <c r="H16" s="53">
-        <v>3</v>
-      </c>
-      <c r="I16" s="61">
-        <v>3</v>
-      </c>
-      <c r="J16" s="53">
-        <v>3</v>
-      </c>
-      <c r="K16" s="53">
+      <c r="D16" s="43">
+        <v>3</v>
+      </c>
+      <c r="E16" s="43">
+        <v>3</v>
+      </c>
+      <c r="F16" s="43">
+        <v>3</v>
+      </c>
+      <c r="G16" s="43">
+        <v>3</v>
+      </c>
+      <c r="H16" s="43">
+        <v>3</v>
+      </c>
+      <c r="I16" s="51">
+        <v>3</v>
+      </c>
+      <c r="J16" s="43">
+        <v>3</v>
+      </c>
+      <c r="K16" s="43">
         <v>3</v>
       </c>
       <c r="L16" s="1"/>
     </row>
     <row r="17" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="52" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -4544,106 +4420,106 @@
       <c r="C17" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="58">
-        <v>3</v>
-      </c>
-      <c r="E17" s="58">
-        <v>3</v>
-      </c>
-      <c r="F17" s="51">
-        <v>3</v>
-      </c>
-      <c r="G17" s="55">
-        <v>3</v>
-      </c>
-      <c r="H17" s="58">
-        <v>3</v>
-      </c>
-      <c r="I17" s="51">
-        <v>3</v>
-      </c>
-      <c r="J17" s="51">
-        <v>3</v>
-      </c>
-      <c r="K17" s="51">
+      <c r="D17" s="48">
+        <v>3</v>
+      </c>
+      <c r="E17" s="48">
+        <v>3</v>
+      </c>
+      <c r="F17" s="41">
+        <v>3</v>
+      </c>
+      <c r="G17" s="45">
+        <v>3</v>
+      </c>
+      <c r="H17" s="48">
+        <v>3</v>
+      </c>
+      <c r="I17" s="41">
+        <v>3</v>
+      </c>
+      <c r="J17" s="41">
+        <v>3</v>
+      </c>
+      <c r="K17" s="41">
         <v>2</v>
       </c>
       <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="42"/>
+      <c r="A18" s="53"/>
       <c r="B18" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="52">
-        <v>3</v>
-      </c>
-      <c r="E18" s="52">
-        <v>2</v>
-      </c>
-      <c r="F18" s="52">
-        <v>3</v>
-      </c>
-      <c r="G18" s="52">
-        <v>3</v>
-      </c>
-      <c r="H18" s="52">
-        <v>3</v>
-      </c>
-      <c r="I18" s="52">
-        <v>3</v>
-      </c>
-      <c r="J18" s="52">
-        <v>3</v>
-      </c>
-      <c r="K18" s="52">
+      <c r="D18" s="42">
+        <v>3</v>
+      </c>
+      <c r="E18" s="42">
+        <v>2</v>
+      </c>
+      <c r="F18" s="42">
+        <v>3</v>
+      </c>
+      <c r="G18" s="42">
+        <v>3</v>
+      </c>
+      <c r="H18" s="42">
+        <v>3</v>
+      </c>
+      <c r="I18" s="42">
+        <v>3</v>
+      </c>
+      <c r="J18" s="42">
+        <v>3</v>
+      </c>
+      <c r="K18" s="42">
         <v>3</v>
       </c>
       <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="43"/>
+      <c r="A19" s="54"/>
       <c r="B19" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="53">
-        <v>3</v>
-      </c>
-      <c r="E19" s="53">
-        <v>3</v>
-      </c>
-      <c r="F19" s="53">
-        <v>3</v>
-      </c>
-      <c r="G19" s="57">
-        <v>3</v>
-      </c>
-      <c r="H19" s="53">
-        <v>3</v>
-      </c>
-      <c r="I19" s="53">
-        <v>3</v>
-      </c>
-      <c r="J19" s="53">
-        <v>3</v>
-      </c>
-      <c r="K19" s="53">
+      <c r="D19" s="43">
+        <v>3</v>
+      </c>
+      <c r="E19" s="43">
+        <v>3</v>
+      </c>
+      <c r="F19" s="43">
+        <v>3</v>
+      </c>
+      <c r="G19" s="47">
+        <v>3</v>
+      </c>
+      <c r="H19" s="43">
+        <v>3</v>
+      </c>
+      <c r="I19" s="43">
+        <v>3</v>
+      </c>
+      <c r="J19" s="43">
+        <v>3</v>
+      </c>
+      <c r="K19" s="43">
         <v>3</v>
       </c>
       <c r="L19" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D21" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E21" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
@@ -4654,7 +4530,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D22">
         <f>COUNTIF(D$5:K$19,B22)</f>
@@ -4670,7 +4546,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D23">
         <f t="shared" ref="D23:D24" si="4">COUNTIF(D$5:K$19,B23)</f>
@@ -4686,7 +4562,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D24">
         <f t="shared" si="4"/>
@@ -4729,29 +4605,29 @@
         <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="46" t="s">
+      <c r="E3" s="56"/>
+      <c r="F3" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="47"/>
-      <c r="H3" s="46" t="s">
+      <c r="G3" s="58"/>
+      <c r="H3" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="47"/>
-      <c r="J3" s="46" t="s">
+      <c r="I3" s="58"/>
+      <c r="J3" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="47"/>
+      <c r="K3" s="58"/>
       <c r="M3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4789,20 +4665,20 @@
         <v>16</v>
       </c>
       <c r="M4" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="N4" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="O4" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="P4" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="N4" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="O4" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="P4" s="38" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="52" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -4853,7 +4729,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="42"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
@@ -4886,7 +4762,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="43"/>
+      <c r="A7" s="54"/>
       <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
@@ -4919,7 +4795,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="59" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -4970,7 +4846,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="49"/>
+      <c r="A9" s="60"/>
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -5003,7 +4879,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="50"/>
+      <c r="A10" s="61"/>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
@@ -5036,7 +4912,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -5087,7 +4963,7 @@
       </c>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="42"/>
+      <c r="A12" s="53"/>
       <c r="B12" s="5" t="s">
         <v>3</v>
       </c>
@@ -5120,7 +4996,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="43"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="6" t="s">
         <v>4</v>
       </c>
@@ -5153,7 +5029,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="52" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -5204,7 +5080,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="42"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="5" t="s">
         <v>3</v>
       </c>
@@ -5237,7 +5113,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="43"/>
+      <c r="A16" s="54"/>
       <c r="B16" s="6" t="s">
         <v>4</v>
       </c>
@@ -5270,7 +5146,7 @@
       </c>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="52" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -5321,7 +5197,7 @@
       </c>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="42"/>
+      <c r="A18" s="53"/>
       <c r="B18" s="5" t="s">
         <v>3</v>
       </c>
@@ -5354,7 +5230,7 @@
       </c>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="43"/>
+      <c r="A19" s="54"/>
       <c r="B19" s="6" t="s">
         <v>4</v>
       </c>
@@ -5406,7 +5282,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B21">
         <f>SUM(D5:K19)/120</f>
@@ -5415,7 +5291,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B22">
         <f>MIN(D5:K19)</f>
@@ -5424,7 +5300,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B23">
         <f>MAX(D5:K19)</f>
@@ -5439,7 +5315,6 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="H3:I3"/>
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A8:A10"/>
@@ -5448,6 +5323,7 @@
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:K19">
     <cfRule type="colorScale" priority="1">
@@ -5481,29 +5357,29 @@
         <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="46" t="s">
+      <c r="E3" s="56"/>
+      <c r="F3" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="47"/>
-      <c r="H3" s="46" t="s">
+      <c r="G3" s="58"/>
+      <c r="H3" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="47"/>
-      <c r="J3" s="46" t="s">
+      <c r="I3" s="58"/>
+      <c r="J3" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="47"/>
+      <c r="K3" s="58"/>
       <c r="M3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5541,20 +5417,20 @@
         <v>16</v>
       </c>
       <c r="M4" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="N4" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="O4" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="P4" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="N4" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="O4" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="P4" s="38" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="52" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -5605,7 +5481,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="42"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
@@ -5638,7 +5514,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="43"/>
+      <c r="A7" s="54"/>
       <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
@@ -5671,7 +5547,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="59" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -5722,7 +5598,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="49"/>
+      <c r="A9" s="60"/>
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -5755,7 +5631,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="50"/>
+      <c r="A10" s="61"/>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
@@ -5788,7 +5664,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -5839,7 +5715,7 @@
       </c>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="42"/>
+      <c r="A12" s="53"/>
       <c r="B12" s="5" t="s">
         <v>3</v>
       </c>
@@ -5872,7 +5748,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="43"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="6" t="s">
         <v>4</v>
       </c>
@@ -5905,7 +5781,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="52" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -5956,7 +5832,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="42"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="5" t="s">
         <v>3</v>
       </c>
@@ -5989,7 +5865,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="43"/>
+      <c r="A16" s="54"/>
       <c r="B16" s="6" t="s">
         <v>4</v>
       </c>
@@ -6022,7 +5898,7 @@
       </c>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="52" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -6073,7 +5949,7 @@
       </c>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="42"/>
+      <c r="A18" s="53"/>
       <c r="B18" s="5" t="s">
         <v>3</v>
       </c>
@@ -6106,7 +5982,7 @@
       </c>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="43"/>
+      <c r="A19" s="54"/>
       <c r="B19" s="6" t="s">
         <v>4</v>
       </c>
@@ -6158,7 +6034,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B21">
         <f>SUM(D5:K19)/120</f>
@@ -6167,7 +6043,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B22">
         <f>MIN(D5:K19)</f>
@@ -6176,7 +6052,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B23">
         <f>MAX(D5:K19)</f>
@@ -6227,29 +6103,29 @@
         <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="46" t="s">
+      <c r="E3" s="56"/>
+      <c r="F3" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="47"/>
-      <c r="H3" s="46" t="s">
+      <c r="G3" s="58"/>
+      <c r="H3" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="47"/>
-      <c r="J3" s="46" t="s">
+      <c r="I3" s="58"/>
+      <c r="J3" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="47"/>
+      <c r="K3" s="58"/>
       <c r="M3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6287,20 +6163,20 @@
         <v>16</v>
       </c>
       <c r="M4" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="N4" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="O4" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="P4" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="N4" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="O4" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="P4" s="38" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="52" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -6351,7 +6227,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="42"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
@@ -6384,7 +6260,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="43"/>
+      <c r="A7" s="54"/>
       <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
@@ -6417,7 +6293,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="59" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -6468,7 +6344,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="49"/>
+      <c r="A9" s="60"/>
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -6501,7 +6377,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="50"/>
+      <c r="A10" s="61"/>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
@@ -6534,7 +6410,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -6585,7 +6461,7 @@
       </c>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="42"/>
+      <c r="A12" s="53"/>
       <c r="B12" s="5" t="s">
         <v>3</v>
       </c>
@@ -6618,7 +6494,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="43"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="6" t="s">
         <v>4</v>
       </c>
@@ -6651,7 +6527,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="52" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -6702,7 +6578,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="42"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="5" t="s">
         <v>3</v>
       </c>
@@ -6735,7 +6611,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="43"/>
+      <c r="A16" s="54"/>
       <c r="B16" s="6" t="s">
         <v>4</v>
       </c>
@@ -6768,7 +6644,7 @@
       </c>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="52" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -6819,7 +6695,7 @@
       </c>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="42"/>
+      <c r="A18" s="53"/>
       <c r="B18" s="5" t="s">
         <v>3</v>
       </c>
@@ -6852,7 +6728,7 @@
       </c>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="43"/>
+      <c r="A19" s="54"/>
       <c r="B19" s="6" t="s">
         <v>4</v>
       </c>
@@ -6904,7 +6780,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="L21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M21" s="28">
         <f>MEDIAN(D5:E19)</f>
@@ -6928,10 +6804,10 @@
         <v>39</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" t="s">
         <v>52</v>
-      </c>
-      <c r="E22" t="s">
-        <v>55</v>
       </c>
       <c r="F22" s="28">
         <f>MEDIAN(D5:K19)</f>
@@ -6940,7 +6816,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="E23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F23" s="28">
         <f>MIN(D5:K19)</f>
@@ -6949,7 +6825,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="E24" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F24" s="28">
         <f>MAX(D5:K19)</f>
